--- a/AI_Actions.xlsx
+++ b/AI_Actions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
   <si>
     <t>DecisionID</t>
   </si>
@@ -56,6 +56,24 @@
   </si>
   <si>
     <t>4b50e7bc-0cde-46a5-9ce2-23c0fd79a29b</t>
+  </si>
+  <si>
+    <t>e53e5d52-5de6-4d48-87ff-d878376683d2</t>
+  </si>
+  <si>
+    <t>41b6400c-5963-46a6-a0ca-d3f20792a2b1</t>
+  </si>
+  <si>
+    <t>a2130a20-316f-41e5-be53-a5e6d7fe23d3</t>
+  </si>
+  <si>
+    <t>3a76db80-695b-47fd-a87f-2a6244cc9aa8</t>
+  </si>
+  <si>
+    <t>e2b5e891-cc1e-4924-a337-ddd2426825bb</t>
+  </si>
+  <si>
+    <t>193233a9-deef-4c05-a443-307e29fcc290</t>
   </si>
   <si>
     <t>FEEDBACK</t>
@@ -433,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.7109375" customWidth="1"/>
@@ -480,19 +498,19 @@
         <v>46109</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H2" s="1">
         <v>46110</v>
@@ -506,19 +524,19 @@
         <v>46109</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H3" s="1">
         <v>46110</v>
@@ -532,19 +550,19 @@
         <v>46109</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H4" s="1">
         <v>46111</v>
@@ -558,19 +576,19 @@
         <v>46109</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H5" s="1">
         <v>46111</v>
@@ -584,19 +602,19 @@
         <v>46109</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H6" s="1">
         <v>46112</v>
@@ -610,22 +628,178 @@
         <v>46109</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H7" s="1">
         <v>46110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46155</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="1">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46155</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="1">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46155</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46155</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46155</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="1">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46155</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="1">
+        <v>46156</v>
       </c>
     </row>
   </sheetData>
